--- a/dados/excel/genero_por_escolaridade.xlsx
+++ b/dados/excel/genero_por_escolaridade.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dados" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$D$28</definedName>
@@ -633,7 +633,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>10/10/2026 14:55</t>
+          <t>12/10/2026 16:30</t>
         </is>
       </c>
     </row>

--- a/dados/excel/genero_por_escolaridade.xlsx
+++ b/dados/excel/genero_por_escolaridade.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$D$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$D$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
@@ -633,7 +633,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>12/10/2026 16:30</t>
+          <t>16/10/2026 19:58</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>3666.506639118457</v>
+        <v>3661.784066713982</v>
       </c>
     </row>
     <row r="5">
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>6436.1192</v>
+        <v>5685.198021582734</v>
       </c>
     </row>
     <row r="6">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>5755.664380305603</v>
+        <v>5737.8643063167</v>
       </c>
     </row>
     <row r="7">
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>3868.750557522123</v>
+        <v>3833.893983637508</v>
       </c>
     </row>
     <row r="8">
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>3166.941729106628</v>
+        <v>4593.980992907801</v>
       </c>
     </row>
     <row r="9">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>4964.534844020797</v>
+        <v>4940.490393820714</v>
       </c>
     </row>
     <row r="10">
@@ -945,32 +945,32 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>indefinido</t>
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>7601.237302631579</v>
+        <v>7584.789859154929</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Medio incompleto</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>3769</v>
+        <v>19</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>4125.062270205995</v>
+        <v>7602.625850178359</v>
       </c>
     </row>
     <row r="13">
@@ -981,14 +981,14 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>indefinido</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>74</v>
+        <v>3747</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>5073.757917555082</v>
+        <v>4125.546330157326</v>
       </c>
     </row>
     <row r="14">
@@ -999,32 +999,32 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>indefinido</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>1610</v>
+        <v>102</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>5901.882658493813</v>
+        <v>4834.319517753047</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>3931</v>
+        <v>1604</v>
       </c>
       <c r="D15" s="15" t="n">
-        <v>1639.598133846392</v>
+        <v>5906.559660203845</v>
       </c>
     </row>
     <row r="16">
@@ -1035,14 +1035,14 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>indefinido</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>44</v>
+        <v>3907</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>2378.938963963964</v>
+        <v>1642.289981930871</v>
       </c>
     </row>
     <row r="17">
@@ -1053,32 +1053,32 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>indefinido</t>
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>974</v>
+        <v>76</v>
       </c>
       <c r="D17" s="15" t="n">
-        <v>2905.084359450427</v>
+        <v>1962.120200381679</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>10687</v>
+        <v>966</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>6273.949586329277</v>
+        <v>2919.089744186047</v>
       </c>
     </row>
     <row r="19">
@@ -1089,14 +1089,14 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>indefinido</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>142</v>
+        <v>10636</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>8028.406695668987</v>
+        <v>6273.05376720145</v>
       </c>
     </row>
     <row r="20">
@@ -1107,32 +1107,32 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>indefinido</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>2236</v>
+        <v>218</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>10919.83821982437</v>
+        <v>7692.262569953817</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>2478</v>
+        <v>2211</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>10692.0785287543</v>
+        <v>10938.40693091773</v>
       </c>
     </row>
     <row r="22">
@@ -1143,14 +1143,14 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>indefinido</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>47</v>
+        <v>2468</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>9931.488874478926</v>
+        <v>10694.71805339688</v>
       </c>
     </row>
     <row r="23">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>indefinido</t>
         </is>
       </c>
       <c r="C23" s="14" t="n">
-        <v>331</v>
+        <v>61</v>
       </c>
       <c r="D23" s="15" t="n">
-        <v>16389.2083712676</v>
+        <v>10118.09979709165</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>100</v>
+        <v>327</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>13696.97279883382</v>
+        <v>16446.52620620792</v>
       </c>
     </row>
     <row r="25">
@@ -1197,14 +1197,14 @@
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>indefinido</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C25" s="14" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D25" s="15" t="n">
-        <v>25644.53973509934</v>
+        <v>13696.97279883382</v>
       </c>
     </row>
     <row r="26">
@@ -1215,32 +1215,32 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>indefinido</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>15395.63915845337</v>
+        <v>21221.47688596491</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Doutorado</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="C27" s="14" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="D27" s="15" t="n">
-        <v>13973.19642969984</v>
+        <v>15481.26703240921</v>
       </c>
     </row>
     <row r="28">
@@ -1251,18 +1251,54 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
+          <t>feminino</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>13967.46851294904</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Doutorado</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>indefinido</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="15" t="n">
+        <v>14072.56333333333</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Doutorado</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
           <t>masculino</t>
         </is>
       </c>
-      <c r="C28" s="10" t="n">
+      <c r="C30" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="D28" s="11" t="n">
+      <c r="D30" s="11" t="n">
         <v>16764.28599437148</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D28"/>
+  <autoFilter ref="A1:D30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>